--- a/out/Attention-MambaAMT_repeat_5_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.8053588248051395</v>
+        <v>2.90780289896909</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.8053588248051395</v>
+        <v>2.90780289896909</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.3110100759941125</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.473179781458244</v>
+        <v>-0.3110100759941125</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.073179781458244</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.073179781458244</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.073179781458244</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.073179781458244</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.3110100759941125</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.473179781458244</v>
+        <v>2.90780289896909</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.073179781458244</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-2.073179781458244</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-2.073179781458244</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.073179781458244</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.073179781458244</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.073179781458244</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.073179781458244</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.073179781458244</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002613199841422029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.336339175438052</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6733148663845712</v>
+        <v>-6.909422050928697e-06</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07767454023522528</v>
+        <v>-0.006622046634711591</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.473179781458244</v>
+        <v>2.90780289896909</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2584033152186847</v>
+        <v>-0.006628956056762603</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.473179781458244</v>
+        <v>2.90780289896909</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2584033152186847</v>
+        <v>-0.006628956056762603</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.073179781458244</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2584033152186847</v>
+        <v>-0.007021946403729496</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>1.207351175368961</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.073179781458244</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2584033152186847</v>
+        <v>2.410084847900545</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.2310130433919766</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.40535882480514</v>
+        <v>3.50780289896909</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.258158551316231</v>
+        <v>1.662997665912066</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.330216264076788</v>
+        <v>0.404641254336724</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.473179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.9194551565424253</v>
+        <v>2.24138068335774</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.18714702602225</v>
+        <v>0.2215965142730651</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.473179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.9631342111631565</v>
+        <v>2.279583245806701</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.07153461902726918</v>
+        <v>0.09152239075715261</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.9187907367337053</v>
+        <v>2.240799604822549</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1138221538571679</v>
+        <v>0.1140295353810926</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.074917720198485</v>
+        <v>2.377351252894476</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0702257638069221</v>
+        <v>0.06865991917185658</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.473179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.101459678374175</v>
+        <v>2.400565357659942</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05554553209331786</v>
+        <v>0.05219999629668826</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.142290376424607</v>
+        <v>2.436276707632976</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02432841787958587</v>
+        <v>0.02308819420832841</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.1353505053579</v>
+        <v>2.430206852760968</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01991331032294752</v>
+        <v>0.01832065596919959</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.473179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.150837736316616</v>
+        <v>2.443752589419045</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.009868815062105695</v>
+        <v>0.009082877796587237</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.150647280096376</v>
+        <v>2.443585372599002</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005778742972840823</v>
+        <v>0.005281017754808877</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.152330462618548</v>
+        <v>2.445057227506459</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.00288547915542069</v>
+        <v>0.002636554277031623</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.152321702825483</v>
+        <v>2.445048938593065</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001422306787004717</v>
+        <v>0.001300090265721293</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.152278901208241</v>
+        <v>2.445010866949819</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0008304096482459243</v>
+        <v>0.0007526471805839212</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.152513877273324</v>
+        <v>2.445215848075224</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002689660778119544</v>
+        <v>0.0002494445929927975</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.152220689288484</v>
+        <v>2.444958129380824</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.000132881406070421</v>
+        <v>0.0001230100953944495</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.152217304549768</v>
+        <v>2.444954545840719</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.929303628546762e-05</v>
+        <v>6.349349164303817e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.152225248415917</v>
+        <v>2.44496089680432</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.09302672124099e-05</v>
+        <v>2.818252625748566e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.152217689291738</v>
+        <v>2.444953648057287</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.727729599553518e-05</v>
+        <v>1.536440521940679e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.15222183466883</v>
+        <v>2.44495671772073</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>4.811828801050598e-06</v>
+        <v>5.309983785801169e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.152213832844412</v>
+        <v>2.444949047999635</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>6.660712319777424e-07</v>
+        <v>9.151487243530285e-07</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.152210728159162</v>
+        <v>2.444945562779327</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.938917334575396e-06</v>
+        <v>-1.814378588387752e-06</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.152206409168012</v>
+        <v>2.444941015467142</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-1.849080618131015e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.152201584995123</v>
+        <v>2.444941105411792</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.152200727061538</v>
+        <v>2.444940247478207</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.152200955382573</v>
+        <v>2.444940475799242</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.152200159718362</v>
+        <v>2.44493968013503</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.152200221987735</v>
+        <v>2.444939742404403</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.152200249663012</v>
+        <v>2.44493977007968</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.152200401877034</v>
+        <v>2.444939922293703</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.152200055936073</v>
+        <v>2.444939576352742</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.152200132043085</v>
+        <v>2.444939652459753</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.152200298094746</v>
+        <v>2.444939818511415</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.152200657873346</v>
+        <v>2.444940178290015</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.152200678629804</v>
+        <v>2.444940199046473</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.152200782412092</v>
+        <v>2.444940302828761</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.152201010733127</v>
+        <v>2.444940531149796</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.152200886194381</v>
+        <v>2.44494040661105</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.152200913869658</v>
+        <v>2.444940434286327</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.152200969220212</v>
+        <v>2.44494048963688</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.152201232135343</v>
+        <v>2.444940752552011</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.152201149109512</v>
+        <v>2.44494066952618</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.152200941544935</v>
+        <v>2.444940461961603</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.152200955382573</v>
+        <v>2.444940475799242</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.152201093758958</v>
+        <v>2.444940614175627</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.152200810087369</v>
+        <v>2.444940330504038</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.152200637116888</v>
+        <v>2.444940157533557</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.1522005333346</v>
+        <v>2.444940053751269</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.152200678629804</v>
+        <v>2.444940199046473</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.152200920788477</v>
+        <v>2.444940441205146</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.152200747817997</v>
+        <v>2.444940268234665</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.152200450308769</v>
+        <v>2.444939970725438</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.152200436471131</v>
+        <v>2.444939956887799</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.152200069773711</v>
+        <v>2.44493959019038</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.152200069773711</v>
+        <v>2.44493959019038</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.152200007504338</v>
+        <v>2.444939527921007</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.15219990372205</v>
+        <v>2.444939424138718</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.152199730751569</v>
+        <v>2.444939251168238</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.152199779183303</v>
+        <v>2.444939299599972</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.152199419404704</v>
+        <v>2.444938939821372</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.152199377891788</v>
+        <v>2.444938898308457</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.152199433242342</v>
+        <v>2.44493895365901</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.152199488592896</v>
+        <v>2.444939009009565</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.152199530105811</v>
+        <v>2.44493905052248</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.152199260271861</v>
+        <v>2.44493878068853</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.152199315622415</v>
+        <v>2.444938836039083</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.473179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.152199460917619</v>
+        <v>2.444938981334288</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.473179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.152199426323523</v>
+        <v>2.444938946740192</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.152199412485885</v>
+        <v>2.444938932902553</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.152199502430534</v>
+        <v>2.444939022847203</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.152199820696219</v>
+        <v>2.444939341112887</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.152199640806919</v>
+        <v>2.444939161223588</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.152199682319834</v>
+        <v>2.444939202736503</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.152199495511715</v>
+        <v>2.444939015928384</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.152199564699907</v>
+        <v>2.444939085116576</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.15219936405415</v>
+        <v>2.444938884470818</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.152199405567065</v>
+        <v>2.444938925983734</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.998251296146564e-06</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.9110100759941124</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.152199433242342</v>
+        <v>2.44493895365901</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_5_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.40535882480514</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.473179781458244</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.5979430258540228</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.073179781458244</v>
+        <v>0.0600086555776079</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.5979430258540228</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.073179781458244</v>
+        <v>0.0600086555776079</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.40535882480514</v>
+        <v>0.0600086555776079</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.0600086555776079</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-2.073179781458244</v>
+        <v>0.0600086555776079</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.0600086555776079</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.40535882480514</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.40535882480514</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.5979430258540228</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.5979430258540228</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.8053588248051395</v>
+        <v>-0.5979430258540228</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.5979430258540228</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.473179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.3979430258540227</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.40535882480514</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002613199841422029</v>
+        <v>-0.0001298461561478907</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.336339175438052</v>
+        <v>0.1671221174911957</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.40535882480514</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6733148663845712</v>
+        <v>0.3345605104190915</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07767454023522528</v>
+        <v>-0.03859536618759665</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.473179781458244</v>
+        <v>-0.3979430258540227</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2584033152186847</v>
+        <v>0.128396905147451</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.473179781458244</v>
+        <v>-1.055894707285653</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2584033152186847</v>
+        <v>0.128396905147451</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2584033152186847</v>
+        <v>0.128396905147451</v>
       </c>
     </row>
     <row r="49">
@@ -39892,17 +39892,17 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.5979430258540228</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2584033152186847</v>
+        <v>0.1283290846537356</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>-0.06328061591894926</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.5979430258540228</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.258158551316231</v>
+        <v>0.06504846873478638</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.330216264076788</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.473179781458244</v>
+        <v>-0.3979430258540227</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.9194551565424253</v>
+        <v>0.06496971435714466</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.18714702602225</v>
+        <v>0.009273633754248563</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.473179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.9631342111631565</v>
+        <v>0.07684471344176075</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.07153461902726918</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.5979430258540228</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.9187907367337053</v>
+        <v>0.0715932691319536</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1138221538571679</v>
+        <v>0.07421111461111389</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.40535882480514</v>
+        <v>-0.5979430258540228</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.074917720198485</v>
+        <v>0.2228275941317079</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0702257638069221</v>
+        <v>0.05000384266651372</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.473179781458244</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.101459678374175</v>
+        <v>0.2485378875070638</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05554553209331786</v>
+        <v>0.04479297984296841</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.40535882480514</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.142290376424607</v>
+        <v>0.2880889031960727</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02432841787958587</v>
+        <v>0.01906144496365477</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.40535882480514</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.1353505053579</v>
+        <v>0.2813664304866663</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01991331032294752</v>
+        <v>0.01703508066985888</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.473179781458244</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.150837736316616</v>
+        <v>0.2963680563333272</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.009868815062105695</v>
+        <v>0.00843335120184526</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.40535882480514</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.150647280096376</v>
+        <v>0.2961834039909479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005778742972840823</v>
+        <v>0.005034509211359512</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.152330462618548</v>
+        <v>0.2978137546094407</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.00288547915542069</v>
+        <v>0.002514754605679756</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.152321702825483</v>
+        <v>0.297805110725218</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001422306787004717</v>
+        <v>0.001237497353466215</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.152278901208241</v>
+        <v>0.2977635080033629</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0008304096482459243</v>
+        <v>0.0007312277483964159</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.152513877273324</v>
+        <v>0.2979906407655445</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002689660778119544</v>
+        <v>0.0002252644476831554</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.152220689288484</v>
+        <v>0.2977063201033142</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.000132881406070421</v>
+        <v>0.0001110029489394232</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.152217304549768</v>
+        <v>0.2977028856642505</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.929303628546762e-05</v>
+        <v>5.829337061275693e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.152225248415917</v>
+        <v>0.2977104313047628</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.09302672124099e-05</v>
+        <v>2.645129519238933e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.40535882480514</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.152217689291738</v>
+        <v>0.2977029482875955</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.727729599553518e-05</v>
+        <v>1.50378099855249e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.9179603370092386</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.15222183466883</v>
+        <v>0.2977065539967872</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>4.811828801050598e-06</v>
+        <v>3.692085796045457e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.152213832844412</v>
+        <v>0.2976988842756927</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>6.660712319777424e-07</v>
+        <v>1.06199729475172e-07</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.152210728159162</v>
+        <v>0.2976953990553851</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.938917334575396e-06</v>
+        <v>-2.218853085826681e-06</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.152206409168012</v>
+        <v>0.2976908517431999</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-1.849080618131015e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.152201584995123</v>
+        <v>0.2976909416878498</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.152200727061538</v>
+        <v>0.297690083754265</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.152200955382573</v>
+        <v>0.2976903120752997</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.152200159718362</v>
+        <v>0.2976895164110879</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.152200221987735</v>
+        <v>0.297689578680461</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.152200249663012</v>
+        <v>0.2976896063557379</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.152200401877034</v>
+        <v>0.2976897585697612</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.152200055936073</v>
+        <v>0.2976894126287994</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.152200132043085</v>
+        <v>0.2976894887358111</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.152200298094746</v>
+        <v>0.2976896547874727</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.152200657873346</v>
+        <v>0.2976900145660727</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.152200678629804</v>
+        <v>0.2976900353225304</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.152200782412092</v>
+        <v>0.297690139104819</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.152201010733127</v>
+        <v>0.2976903674258536</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.152200886194381</v>
+        <v>0.2976902428871074</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.152200913869658</v>
+        <v>0.2976902705623843</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.152200969220212</v>
+        <v>0.2976903259129382</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.152201232135343</v>
+        <v>0.2976905888280689</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.152201149109512</v>
+        <v>0.2976905058022381</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.152200941544935</v>
+        <v>0.2976902982376614</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.152200955382573</v>
+        <v>0.2976903120752997</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.152201093758958</v>
+        <v>0.2976904504516844</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.152200810087369</v>
+        <v>0.2976901667800958</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.152200637116888</v>
+        <v>0.297689993809615</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.1522005333346</v>
+        <v>0.2976898900273265</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.152200678629804</v>
+        <v>0.2976900353225304</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.152200920788477</v>
+        <v>0.2976902774812037</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.152200747817997</v>
+        <v>0.2976901045107227</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.152200450308769</v>
+        <v>0.2976898070014957</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.152200436471131</v>
+        <v>0.2976897931638572</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.152200069773711</v>
+        <v>0.297689426466438</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.7179603370092386</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.152200069773711</v>
+        <v>0.297689426466438</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.8053588248051395</v>
+        <v>0.0600086555776079</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.152200007504338</v>
+        <v>0.2976893641970649</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.5979430258540228</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.15219990372205</v>
+        <v>0.2976892604147764</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.152199730751569</v>
+        <v>0.2976890874442956</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.152199779183303</v>
+        <v>0.2976891358760302</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.152199419404704</v>
+        <v>0.2976887760974302</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.152199377891788</v>
+        <v>0.2976887345845147</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.152199433242342</v>
+        <v>0.2976887899350685</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.152199488592896</v>
+        <v>0.2976888452856224</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.073179781458244</v>
+        <v>-0.5979430258540228</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.152199530105811</v>
+        <v>0.2976888867985378</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.40535882480514</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.152199260271861</v>
+        <v>0.2976886169645877</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.40535882480514</v>
+        <v>0.2600086555776079</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.152199315622415</v>
+        <v>0.2976886723151417</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.473179781458244</v>
+        <v>-0.3979430258540227</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.152199460917619</v>
+        <v>0.2976888176103455</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.473179781458244</v>
+        <v>-1.055894707285653</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.152199426323523</v>
+        <v>0.2976887830162493</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.152199412485885</v>
+        <v>0.2976887691786108</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.152199502430534</v>
+        <v>0.2976888591232609</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.152199820696219</v>
+        <v>0.2976891773889456</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.152199640806919</v>
+        <v>0.2976889974996454</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.152199682319834</v>
+        <v>0.2976890390125608</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.152199495511715</v>
+        <v>0.2976888522044416</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.152199564699907</v>
+        <v>0.297688921392634</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.15219936405415</v>
+        <v>0.2976887207468762</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.152199405567065</v>
+        <v>0.2976887622597916</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-3.998251296146564e-06</v>
+        <v>-4.27818704739785e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-2.073179781458244</v>
+        <v>-1.255894707285654</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.152199433242342</v>
+        <v>0.2976887899350685</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_5_000006.xlsx
+++ b/out/Attention-MambaAMT_repeat_5_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.02208256721496582</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.007595233619213104</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.51</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.001709446310997009</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.2600086555776079</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.0002633407711982727</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.2600086555776079</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.004040069878101349</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5979430258540228</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.002282969653606415</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.0600086555776079</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.007327847182750702</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5979430258540228</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.007622033357620239</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.0600086555776079</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>5.655735731124878e-05</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.0600086555776079</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.006153710186481476</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.9179603370092386</v>
+        <v>0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.01723286509513855</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.9179603370092386</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.01902908086776733</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.9179603370092386</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.01296355575323105</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.9179603370092386</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.01157509535551071</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.9179603370092386</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.01913911104202271</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.9179603370092386</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.02021054923534393</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.9179603370092386</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.01169025152921677</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.9179603370092386</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001366719603538513</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.0600086555776079</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-8.866190910339355e-07</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.0600086555776079</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.002186097204685211</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.0600086555776079</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.005823232233524323</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.01679559051990509</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.01582427322864532</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.9179603370092386</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.0006075054407119751</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.9179603370092386</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.005394093692302704</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.9179603370092386</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.001607142388820648</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.2600086555776079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0006357282400131226</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.5979430258540228</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.03647341579198837</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.01223243772983551</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.003880865871906281</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.002772517502307892</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.5979430258540228</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.007908716797828674</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5979430258540228</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0002709701657295227</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5979430258540228</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.01027613133192062</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.01213055849075317</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.01481002569198608</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.005961842834949493</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.009583286941051483</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0159747451543808</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.01722992956638336</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.01284109801054001</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.01037254184484482</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3979430258540227</v>
+        <v>0.16</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01959509402513504</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.2600086555776079</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001298461561478907</v>
+        <v>-0.000118366278514266</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1671221174911957</v>
+        <v>0.15234641027499</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01274652406573296</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.2600086555776079</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3345605104190915</v>
+        <v>0.3049815551255529</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.03859536618759665</v>
+        <v>-0.03518314527081071</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.02746041119098663</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3979430258540227</v>
+        <v>0.16</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.128396905147451</v>
+        <v>0.1170448987256652</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.009246639907360077</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.055894707285653</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.128396905147451</v>
+        <v>0.1170448987256652</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.005387924611568451</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.128396905147451</v>
+        <v>0.1169576697818758</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.2679861802650542</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01360299438238144</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5979430258540228</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.1283290846537356</v>
+        <v>0.6534636534327469</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>-0.06328061591894926</v>
+        <v>0.05127613601825678</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.007903918623924255</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5979430258540228</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.06504846873478638</v>
+        <v>0.4876386718199176</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.08981479763008771</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.009450711309909821</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3979430258540227</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.06496971435714466</v>
+        <v>0.6160177017088593</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.009273633754248563</v>
+        <v>0.04918585159622395</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.005128629505634308</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.07684471344176075</v>
+        <v>0.6244972338553442</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.02031447301693191</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01572916656732559</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5979430258540228</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.0715932691319536</v>
+        <v>0.6158886831624538</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07421111461111389</v>
+        <v>0.02531058052856254</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.03249791264533997</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5979430258540228</v>
+        <v>0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2228275941317079</v>
+        <v>0.6461983873393731</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.05000384266651372</v>
+        <v>0.01523963656693178</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.008406579494476318</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.2600086555776079</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2485378875070638</v>
+        <v>0.6513510981034867</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.04479297984296841</v>
+        <v>0.01158491540213203</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.04694492742419243</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.2600086555776079</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2880889031960727</v>
+        <v>0.6592766984452065</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01906144496365477</v>
+        <v>0.005122056203503378</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.0169738382101059</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.2600086555776079</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2813664304866663</v>
+        <v>0.6579259225037994</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01703508066985888</v>
+        <v>0.0040633276547783</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.001636706292629242</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2600086555776079</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2963680563333272</v>
+        <v>0.6609290448934634</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.00843335120184526</v>
+        <v>0.002011193092223868</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.06450300663709641</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.2600086555776079</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2961834039909479</v>
+        <v>0.6608880400942727</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005034509211359512</v>
+        <v>0.001167407900488705</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.04945402219891548</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.9179603370092386</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2978137546094407</v>
+        <v>0.6612110061074167</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002514754605679756</v>
+        <v>0.0005826585506171673</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.03016902133822441</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.9179603370092386</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.297805110725218</v>
+        <v>0.6612052744328513</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001237497353466215</v>
+        <v>0.0002853394644005519</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.02282067760825157</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.9179603370092386</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2977635080033629</v>
+        <v>0.6611929247809478</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0007312277483964159</v>
+        <v>0.0001618826388951368</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.0428675040602684</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.9179603370092386</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2979906407655445</v>
+        <v>0.6612345375851219</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002252644476831554</v>
+        <v>5.079925284929769e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.009832531213760376</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.9179603370092386</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2977063201033142</v>
+        <v>0.6611730098077292</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001110029489394232</v>
+        <v>2.419528491452356e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01833690702915192</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9179603370092386</v>
+        <v>-0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2977028856642505</v>
+        <v>0.6611683328599858</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>5.829337061275693e-05</v>
+        <v>9.677176780651038e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.0166882611811161</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9179603370092386</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2977104313047628</v>
+        <v>0.661165922859567</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.645129519238933e-05</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.0220714695751667</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9179603370092386</v>
+        <v>-0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2977029482875955</v>
+        <v>0.6611603811868366</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.50378099855249e-05</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.03108683228492737</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9179603370092386</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2977065539967872</v>
+        <v>0.6611575326141347</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>3.692085796045457e-06</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01801436021924019</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7179603370092386</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2976988842756927</v>
+        <v>0.661151865183861</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>1.06199729475172e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.02957813069224358</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7179603370092386</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2976953990553851</v>
+        <v>0.6611522457189187</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-2.218853085826681e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.02619167789816856</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.7179603370092386</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2976908517431999</v>
+        <v>0.6611524740399535</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.03160203248262405</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.7179603370092386</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2976909416878498</v>
+        <v>0.6611525639846034</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.01562454923987389</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.7179603370092386</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.297690083754265</v>
+        <v>0.6611517060510186</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.02558008581399918</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7179603370092386</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2976903120752997</v>
+        <v>0.6611519343720532</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.01706071570515633</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2976895164110879</v>
+        <v>0.6611511387078415</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.00580412894487381</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.297689578680461</v>
+        <v>0.6611512009772146</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.004994302988052368</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2976896063557379</v>
+        <v>0.6611512286524914</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.011093370616436</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2976897585697612</v>
+        <v>0.6611513808665147</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.004045896232128143</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2976894126287994</v>
+        <v>0.661151034925553</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.009538926184177399</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2976894887358111</v>
+        <v>0.6611511110325646</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.009452678263187408</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2976896547874727</v>
+        <v>0.6611512770842263</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01560287177562714</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2976900145660727</v>
+        <v>0.6611516368628263</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.01746927574276924</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2976900353225304</v>
+        <v>0.661151657619284</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01800356805324554</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.297690139104819</v>
+        <v>0.6611517614015725</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.0133061371743679</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2976903674258536</v>
+        <v>0.6611519897226071</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.01486948132514954</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2976902428871074</v>
+        <v>0.661151865183861</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01157458499073982</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7179603370092386</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2976902705623843</v>
+        <v>0.6611518928591379</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.02256875112652779</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7179603370092386</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2976903259129382</v>
+        <v>0.6611519482096918</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.01901408284902573</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7179603370092386</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2976905888280689</v>
+        <v>0.6611522111248225</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01641663163900375</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7179603370092386</v>
+        <v>0.16</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2976905058022381</v>
+        <v>0.6611521280989917</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.01640224456787109</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2976902982376614</v>
+        <v>0.661151920534415</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01720603927969933</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2976903120752997</v>
+        <v>0.6611519343720532</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.01572893559932709</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2976904504516844</v>
+        <v>0.661152072748438</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01501023024320602</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2976901667800958</v>
+        <v>0.6611517890768493</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.007109574973583221</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.297689993809615</v>
+        <v>0.6611516161063686</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.01433435082435608</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2976898900273265</v>
+        <v>0.6611515123240801</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.01401538774371147</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2976900353225304</v>
+        <v>0.661151657619284</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.0119788646697998</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2976902774812037</v>
+        <v>0.6611518997779572</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.01505421102046967</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2976901045107227</v>
+        <v>0.6611517268074762</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.006941966712474823</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2976898070014957</v>
+        <v>0.6611514292982493</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.0134953111410141</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2976897931638572</v>
+        <v>0.6611514154606107</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.004679284989833832</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.297689426466438</v>
+        <v>0.6611510487631915</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.002920188009738922</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7179603370092386</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.297689426466438</v>
+        <v>0.6611510487631915</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.008856616914272308</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.0600086555776079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2976893641970649</v>
+        <v>0.6611509864938184</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.006781034171581268</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5979430258540228</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2976892604147764</v>
+        <v>0.66115088271153</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.002737723290920258</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2976890874442956</v>
+        <v>0.6611507097410492</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.004059292376041412</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2976891358760302</v>
+        <v>0.6611507581727838</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.002612024545669556</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2976887760974302</v>
+        <v>0.6611503983941838</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.004316076636314392</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2976887345845147</v>
+        <v>0.6611503568812683</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.001211203634738922</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2976887899350685</v>
+        <v>0.661150412231822</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.003106124699115753</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2976888452856224</v>
+        <v>0.6611504675823759</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.002316422760486603</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5979430258540228</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2976888867985378</v>
+        <v>0.6611505090952914</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.004802703857421875</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.2600086555776079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2976886169645877</v>
+        <v>0.6611502392613413</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.001191899180412292</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.2600086555776079</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2976886723151417</v>
+        <v>0.6611502946118952</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.002527289092540741</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3979430258540227</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2976888176103455</v>
+        <v>0.6611504399070991</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.001015692949295044</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.055894707285653</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2976887830162493</v>
+        <v>0.6611504053130028</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.002034910023212433</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2976887691786108</v>
+        <v>0.6611503914753644</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003767140209674835</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2976888591232609</v>
+        <v>0.6611504814200145</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.0017123743891716</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2976891773889456</v>
+        <v>0.6611507996856991</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01826505362987518</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2976889974996454</v>
+        <v>0.661150619796399</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.01597391068935394</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2976890390125608</v>
+        <v>0.6611506613093144</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.006327793002128601</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2976888522044416</v>
+        <v>0.6611504745011951</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.007224120199680328</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.297688921392634</v>
+        <v>0.6611505436893876</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.004729293286800385</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2976887207468762</v>
+        <v>0.6611503430436297</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.005858533084392548</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2976887622597916</v>
+        <v>0.6611503845565452</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.27818704739785e-06</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.008896499872207642</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.255894707285654</v>
+        <v>-0.3999999999999995</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2976887899350685</v>
+        <v>0.661150412231822</v>
       </c>
     </row>
   </sheetData>
